--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484183_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484183_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. POU BLINNIKOV</t>
+          <t>M. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5275</v>
+        <v>6.0565</v>
       </c>
       <c r="E2" t="n">
-        <v>2.639</v>
+        <v>2.6221</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8885</v>
+        <v>3.4344</v>
       </c>
       <c r="G2" t="n">
-        <v>1.4759</v>
+        <v>3.9745</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0507</v>
+        <v>-0.3474</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4252</v>
+        <v>4.3219</v>
       </c>
       <c r="J2" t="n">
-        <v>1.0894</v>
+        <v>3.9257</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3639</v>
+        <v>0.3035</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7255</v>
+        <v>3.6222</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3865</v>
+        <v>0.0488</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3132</v>
+        <v>-0.6509</v>
       </c>
       <c r="O2" t="n">
         <v>0.6997</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1822</v>
+        <v>1.3887</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1822</v>
+        <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2661</v>
+        <v>0.9593</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6803</v>
+        <v>-0.3116</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5858</v>
+        <v>1.271</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6032</v>
+        <v>-0.266</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>-0.266</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. GARCIA CALVO</t>
+          <t>A. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3608</v>
+        <v>5.7634</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0667</v>
+        <v>1.9871</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2941</v>
+        <v>3.7763</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9745</v>
+        <v>1.4759</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3474</v>
+        <v>0.0507</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3219</v>
+        <v>1.4252</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9257</v>
+        <v>1.0894</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3035</v>
+        <v>0.3639</v>
       </c>
       <c r="L3" t="n">
-        <v>3.6222</v>
+        <v>0.7255</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0488</v>
+        <v>0.3865</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6509</v>
+        <v>-0.3132</v>
       </c>
       <c r="O3" t="n">
         <v>0.6997</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3887</v>
+        <v>2.1822</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3806</v>
+        <v>2.1822</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2636</v>
+        <v>1.5021</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8671</v>
+        <v>0.0285</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1307</v>
+        <v>1.4736</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.266</v>
+        <v>0.6032</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X3" t="n">
         <v>-0.266</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. AGUILERA MELCHOR</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3981</v>
+        <v>2.8437</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4084</v>
+        <v>-1.6538</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9897</v>
+        <v>4.4975</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0635</v>
+        <v>2.2617</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1944</v>
+        <v>1.9003</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1309</v>
+        <v>0.3615</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0395</v>
+        <v>1.2883</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6356000000000001</v>
+        <v>1.2054</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6751</v>
+        <v>0.0829</v>
       </c>
       <c r="M4" t="n">
-        <v>1.103</v>
+        <v>0.9734</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5588</v>
+        <v>0.6949</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5442</v>
+        <v>0.2786</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7935</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7855</v>
+        <v>1.9838</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7476</v>
+        <v>0.6334</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4398</v>
+        <v>-0.2323</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3077</v>
+        <v>0.8657</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2065</v>
+        <v>0.9405</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2065</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3535</v>
+        <v>2.7562</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2238</v>
+        <v>-0.7931</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5774</v>
+        <v>3.5493</v>
       </c>
       <c r="G5" t="n">
         <v>0.8139</v>
@@ -844,13 +844,13 @@
         <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4801</v>
+        <v>0.8828</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6744</v>
+        <v>-0.2437</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1545</v>
+        <v>1.1264</v>
       </c>
       <c r="V5" t="n">
         <v>0.266</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>A. AGUILERA MELCHOR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3288</v>
+        <v>1.6071</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0846</v>
+        <v>-0.6912</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4133</v>
+        <v>2.2983</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2617</v>
+        <v>1.0635</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9003</v>
+        <v>1.1944</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3615</v>
+        <v>-0.1309</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2883</v>
+        <v>-0.0395</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2054</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0829</v>
+        <v>-0.6751</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9734</v>
+        <v>1.103</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6949</v>
+        <v>0.5588</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2786</v>
+        <v>0.5442</v>
       </c>
       <c r="P6" t="n">
+        <v>0.7935</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-0.9919</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-2.9758</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.9838</v>
+        <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1185</v>
+        <v>0.9565</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6631</v>
+        <v>0.3402</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7816</v>
+        <v>0.6163</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9405</v>
+        <v>-1.2065</v>
       </c>
       <c r="W6" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6745</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2194</v>
+        <v>1.5993</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1068</v>
+        <v>-1.3903</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3263</v>
+        <v>2.9896</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6185</v>
@@ -1000,13 +1000,13 @@
         <v>1.7855</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6234</v>
+        <v>1.0033</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0511</v>
+        <v>-0.2323</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5722</v>
+        <v>1.2356</v>
       </c>
       <c r="V7" t="n">
         <v>2.4129</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4275</v>
+        <v>1.5179</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3436</v>
+        <v>1.406</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0839</v>
+        <v>0.112</v>
       </c>
       <c r="G8" t="n">
         <v>0.8619</v>
@@ -1078,13 +1078,13 @@
         <v>0.3968</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1683</v>
+        <v>-0.0779</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.187</v>
+        <v>-0.1247</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V8" t="n">
         <v>0.3373</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2623</v>
+        <v>1.2801</v>
       </c>
       <c r="E9" t="n">
-        <v>2.526</v>
+        <v>2.628</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2637</v>
+        <v>-1.3479</v>
       </c>
       <c r="G9" t="n">
         <v>3.2969</v>
@@ -1156,13 +1156,13 @@
         <v>1.1903</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0572</v>
+        <v>0.0751</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6121</v>
+        <v>-0.5101</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6693</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>-3.2821</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.534</v>
+        <v>0.7763</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0859</v>
+        <v>-0.9839</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6199</v>
+        <v>1.7602</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1539</v>
@@ -1234,13 +1234,13 @@
         <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2409</v>
+        <v>0.0014</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3004</v>
+        <v>-0.1983</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0595</v>
+        <v>0.1997</v>
       </c>
       <c r="V10" t="n">
         <v>0.532</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9111</v>
+        <v>0.0502</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7629</v>
+        <v>-2.0261</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8518</v>
+        <v>2.0763</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2106</v>
@@ -1312,13 +1312,13 @@
         <v>1.5871</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6212</v>
+        <v>0.3401</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1846</v>
+        <v>-0.4477</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5633</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6745</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5953</v>
+        <v>-2.3865</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9154</v>
+        <v>-2.7907</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3201</v>
+        <v>0.4043</v>
       </c>
       <c r="G12" t="n">
         <v>-0.951</v>
@@ -1390,13 +1390,13 @@
         <v>0.5952</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2556</v>
+        <v>-0.0468</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3117</v>
+        <v>-0.187</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0561</v>
+        <v>0.1403</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6989</v>
+        <v>-2.4109</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2553</v>
+        <v>-3.5184</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5563</v>
+        <v>1.1075</v>
       </c>
       <c r="G13" t="n">
         <v>-1.1425</v>
@@ -1468,13 +1468,13 @@
         <v>1.7855</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1145</v>
+        <v>0.4024</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4226</v>
+        <v>-0.6857</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5371</v>
+        <v>1.0882</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4724</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.20659999999999</v>
+        <v>19.45330000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.451000000000001</v>
+        <v>-5.2043</v>
       </c>
       <c r="F14" t="n">
-        <v>24.6576</v>
+        <v>24.6578</v>
       </c>
       <c r="G14" t="n">
         <v>9.671799999999999</v>
@@ -1528,16 +1528,16 @@
         <v>2.460799999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>4.0543</v>
+        <v>4.054299999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5232999999999995</v>
+        <v>0.5232999999999998</v>
       </c>
       <c r="O14" t="n">
         <v>3.5311</v>
       </c>
       <c r="P14" t="n">
-        <v>4.959599999999999</v>
+        <v>4.9596</v>
       </c>
       <c r="Q14" t="n">
         <v>-12.8948</v>
@@ -1546,13 +1546,13 @@
         <v>17.8548</v>
       </c>
       <c r="S14" t="n">
-        <v>5.384999999999999</v>
+        <v>6.6317</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.0518</v>
+        <v>-2.8047</v>
       </c>
       <c r="U14" t="n">
-        <v>9.436500000000001</v>
+        <v>9.436600000000002</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8096</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6807</v>
+        <v>0.5965</v>
       </c>
       <c r="E15" t="n">
         <v>-0.0422</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7228</v>
+        <v>0.6387</v>
       </c>
       <c r="G15" t="n">
         <v>0.2267</v>
@@ -1624,13 +1624,13 @@
         <v>0.1984</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2556</v>
+        <v>0.1714</v>
       </c>
       <c r="T15" t="n">
         <v>-0.0623</v>
       </c>
       <c r="U15" t="n">
-        <v>0.318</v>
+        <v>0.2338</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2644</v>
+        <v>0.3188</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2421</v>
+        <v>-0.064</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0223</v>
+        <v>0.3828</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0977</v>
@@ -1702,13 +1702,13 @@
         <v>1.5871</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9443</v>
+        <v>-0.8899</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1278</v>
+        <v>-1.4339</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1835</v>
+        <v>0.544</v>
       </c>
       <c r="V16" t="n">
         <v>3.8854</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1915</v>
+        <v>-0.0478</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1254</v>
+        <v>-1.9214</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9339</v>
+        <v>1.8736</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7464</v>
@@ -1780,13 +1780,13 @@
         <v>1.3887</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1581</v>
+        <v>0.3018</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4988</v>
+        <v>-0.2947</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6569</v>
+        <v>0.5965</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3147</v>
+        <v>-0.5868</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4815</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7962</v>
+        <v>-0.6602</v>
       </c>
       <c r="G18" t="n">
         <v>0.7128</v>
@@ -1858,13 +1858,13 @@
         <v>0.7935</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0113</v>
+        <v>-0.2834</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1926</v>
+        <v>-0.6008</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1813</v>
+        <v>0.3173</v>
       </c>
       <c r="V18" t="n">
         <v>-1.8097</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9197</v>
+        <v>-1.0617</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8989</v>
+        <v>-1.2049</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0208</v>
+        <v>0.1432</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1571</v>
@@ -1936,13 +1936,13 @@
         <v>0.9919</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2307</v>
+        <v>-0.3727</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.255</v>
+        <v>-0.5611</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0243</v>
+        <v>0.1884</v>
       </c>
       <c r="V19" t="n">
         <v>-0.532</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5502</v>
+        <v>-1.1718</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6786</v>
+        <v>-3.5766</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1285</v>
+        <v>2.4048</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0566</v>
@@ -2014,13 +2014,13 @@
         <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5016</v>
+        <v>-0.1233</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.8955</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4959</v>
+        <v>0.7722</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6394</v>
+        <v>-1.9318</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7125</v>
+        <v>-1.9166</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0731</v>
+        <v>-0.0153</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6031</v>
@@ -2092,13 +2092,13 @@
         <v>1.1903</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2347</v>
+        <v>-0.5271</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7537</v>
+        <v>-0.9578</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5191</v>
+        <v>0.4307</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9387</v>
+        <v>-2.3605</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5948</v>
+        <v>-3.2887</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6561</v>
+        <v>0.9281</v>
       </c>
       <c r="G22" t="n">
         <v>-0.618</v>
@@ -2170,13 +2170,13 @@
         <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.2267</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4963</v>
+        <v>-1.1902</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6914</v>
+        <v>0.9635</v>
       </c>
       <c r="V22" t="n">
         <v>0.0713</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0745</v>
+        <v>-2.9588</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4739</v>
+        <v>-4.2699</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3995</v>
+        <v>1.3111</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2729</v>
@@ -2248,13 +2248,13 @@
         <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8015</v>
+        <v>-0.6859</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.5586</v>
+        <v>-1.3546</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7571</v>
+        <v>0.6687</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4202</v>
+        <v>-3.1311</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6826</v>
+        <v>-2.5806</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7375</v>
+        <v>-0.5505</v>
       </c>
       <c r="G24" t="n">
         <v>-0.7468</v>
@@ -2326,13 +2326,13 @@
         <v>0.7935</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0231</v>
+        <v>-0.734</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8728</v>
+        <v>-0.7708</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1503</v>
+        <v>0.0368</v>
       </c>
       <c r="V24" t="n">
         <v>0.532</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.1028</v>
+        <v>-4.4642</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.1723</v>
+        <v>-5.8663</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0696</v>
+        <v>1.402</v>
       </c>
       <c r="G25" t="n">
         <v>-4.3126</v>
@@ -2404,13 +2404,13 @@
         <v>1.9838</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2464</v>
+        <v>-0.6079</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.621</v>
+        <v>-1.3149</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3746</v>
+        <v>0.707</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3373</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.2066</v>
+        <v>-16.7992</v>
       </c>
       <c r="E26" t="n">
-        <v>-24.6576</v>
+        <v>-24.6578</v>
       </c>
       <c r="F26" t="n">
-        <v>6.4513</v>
+        <v>7.858300000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-9.6717</v>
@@ -2482,13 +2482,13 @@
         <v>12.8949</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.3848</v>
+        <v>-3.9777</v>
       </c>
       <c r="T26" t="n">
-        <v>-9.436400000000001</v>
+        <v>-9.436599999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>4.0518</v>
+        <v>5.458900000000001</v>
       </c>
       <c r="V26" t="n">
         <v>1.8097</v>
